--- a/Output/final_transactions.xlsx
+++ b/Output/final_transactions.xlsx
@@ -667,7 +667,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>MR  RAVI</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>INDIAN O</t>
+          <t>FUEL</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Fuel</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>VIKAS PH</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>INDIAN O</t>
+          <t>FUEL</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>Others</t>
+          <t>Fuel</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -6088,7 +6088,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>Bills Payment</t>
+          <t>Others</t>
         </is>
       </c>
     </row>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -6995,7 +6995,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>MR  RAVI</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -7950,7 +7950,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>VI</t>
+          <t>MR  RAVI</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -8337,7 +8337,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -8703,7 +8703,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -8947,7 +8947,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -9008,7 +9008,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>Daily Exp</t>
+          <t>Daily Utility</t>
         </is>
       </c>
     </row>
